--- a/per-stock/AMAT/financials.xlsx
+++ b/per-stock/AMAT/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>346505936896</v>
+        <v>489960275968</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>344890277888</v>
+        <v>488987295744</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>41.151745</v>
+        <v>58.163055</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27.439754</v>
+        <v>37.95211</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>11.938601</v>
+        <v>16.88121</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -696,7 +705,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6455000064</v>
+        <v>7267999744</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -711,11 +720,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3154374912</v>
+        <v>5343000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>793609867</v>
+        <v>793959430</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>436.62</v>
+        <v>617.11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -790,960 +799,465 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Line item</t>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>FY-3</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>FY-2</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>FY-1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2022-10-31</t>
+          <t>TTM</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2021-10-31</t>
+          <t>Source / formula</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Tax Effect Of Unusual Items</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>-44345000</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>564000</v>
-      </c>
-      <c r="F2" s="3" t="n"/>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-10-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Tax Rate For Calcs</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="F3" s="3" t="n"/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D46</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C46</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B46</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Normalized EBITDA</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>10156000000</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>8791000000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>8469000000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>8267000000</v>
-      </c>
-      <c r="F4" s="3" t="n"/>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D44</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C44</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B44</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Total Unusual Items</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>-181000000</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="F5" s="3" t="n"/>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Total Unusual Items Excluding Goodwill</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>-181000000</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="F6" s="3" t="n"/>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D37</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C37</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B37</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B37:E37)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Net Income From Continuing Operation Net Minority Interest</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F7" s="3" t="n"/>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reconciled Depreciation</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>435000000</v>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>392000000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>515000000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>444000000</v>
-      </c>
-      <c r="F8" s="3" t="n"/>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reconciled Cost Of Revenue</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>14560000000</v>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>14279000000</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>14133000000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>13792000000</v>
-      </c>
-      <c r="F9" s="3" t="n"/>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>9975000000</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>8791000000</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>8469000000</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>8271000000</v>
-      </c>
-      <c r="F10" s="3" t="n"/>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EBIT</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>9540000000</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>8399000000</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>7954000000</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>7827000000</v>
-      </c>
-      <c r="F11" s="3" t="n"/>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B7:E7)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Net Interest Income</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>982000000</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-189000000</v>
-      </c>
-      <c r="F12" s="3" t="n"/>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
-        <v>269000000</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>247000000</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>238000000</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>228000000</v>
-      </c>
-      <c r="F13" s="3" t="n"/>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Interest Income</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
-        <v>1251000000</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>532000000</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="F14" s="3" t="n"/>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Normalized Income</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
-        <v>7134655000</v>
-      </c>
-      <c r="C15" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>6521564000</v>
-      </c>
-      <c r="F15" s="3" t="n"/>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Net Income From Continuing And Discontinued Operation</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Total Expenses</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>19898000000</v>
-      </c>
-      <c r="C17" s="3" t="n">
-        <v>19309000000</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v>18863000000</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>18001000000</v>
-      </c>
-      <c r="F17" s="3" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Total Operating Income As Reported</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>8289000000</v>
-      </c>
-      <c r="C18" s="3" t="n">
-        <v>7867000000</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v>7654000000</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>7788000000</v>
-      </c>
-      <c r="F18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Diluted Average Shares</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>808000000</v>
-      </c>
-      <c r="C19" s="3" t="n">
-        <v>834000000</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v>845000000</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>877000000</v>
-      </c>
-      <c r="F19" s="3" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Basic Average Shares</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="n">
-        <v>804000000</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>827000000</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>840000000</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>871000000</v>
-      </c>
-      <c r="F20" s="3" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Diluted EPS</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="n">
-        <v>8.66</v>
-      </c>
-      <c r="C21" s="3" t="n">
-        <v>8.609999999999999</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>8.109999999999999</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>7.44</v>
-      </c>
-      <c r="F21" s="3" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Basic EPS</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="C22" s="3" t="n">
-        <v>8.68</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>8.16</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="F22" s="3" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Diluted NI Availto Com Stockholders</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F23" s="3" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Net Income Common Stockholders</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E24" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F24" s="3" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Net Income</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Net Income Including Noncontrolling Interests</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Net Income Continuous Operations</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="n">
-        <v>6998000000</v>
-      </c>
-      <c r="C27" s="3" t="n">
-        <v>7177000000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>6856000000</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>6525000000</v>
-      </c>
-      <c r="F27" s="3" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Tax Provision</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="n">
-        <v>2273000000</v>
-      </c>
-      <c r="C28" s="3" t="n">
-        <v>975000000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>860000000</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>1074000000</v>
-      </c>
-      <c r="F28" s="3" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Pretax Income</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="n">
-        <v>9271000000</v>
-      </c>
-      <c r="C29" s="3" t="n">
-        <v>8152000000</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>7716000000</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>7599000000</v>
-      </c>
-      <c r="F29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Other Income Expense</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="n">
-        <v>-181000000</v>
-      </c>
-      <c r="C30" s="3" t="n"/>
-      <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>-311000000</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Special Income Charges</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="n">
-        <v>-181000000</v>
-      </c>
-      <c r="C31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>4000000</v>
-      </c>
-      <c r="F31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Other Special Charges</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n"/>
-      <c r="D32" s="3" t="n"/>
-      <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n">
-        <v>154000000</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Restructuring And Mergern Acquisition</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="n">
-        <v>181000000</v>
-      </c>
-      <c r="C33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>-4000000</v>
-      </c>
-      <c r="F33" s="3" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Net Non Operating Interest Income Expense</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="n">
-        <v>982000000</v>
-      </c>
-      <c r="C34" s="3" t="n">
-        <v>285000000</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>62000000</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-189000000</v>
-      </c>
-      <c r="F34" s="3" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Interest Expense Non Operating</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="n">
-        <v>269000000</v>
-      </c>
-      <c r="C35" s="3" t="n">
-        <v>247000000</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>238000000</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>228000000</v>
-      </c>
-      <c r="F35" s="3" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Interest Income Non Operating</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="n">
-        <v>1251000000</v>
-      </c>
-      <c r="C36" s="3" t="n">
-        <v>532000000</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>39000000</v>
-      </c>
-      <c r="F36" s="3" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Operating Income</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="n">
-        <v>8470000000</v>
-      </c>
-      <c r="C37" s="3" t="n">
-        <v>7867000000</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>7654000000</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>7784000000</v>
-      </c>
-      <c r="F37" s="3" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Operating Expense</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="n">
-        <v>5338000000</v>
-      </c>
-      <c r="C38" s="3" t="n">
-        <v>5030000000</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>4730000000</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>4209000000</v>
-      </c>
-      <c r="F38" s="3" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Research And Development</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="n">
-        <v>3570000000</v>
-      </c>
-      <c r="C39" s="3" t="n">
-        <v>3233000000</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>3102000000</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>2771000000</v>
-      </c>
-      <c r="F39" s="3" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Selling General And Administration</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="n">
-        <v>1768000000</v>
-      </c>
-      <c r="C40" s="3" t="n">
-        <v>1797000000</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>1628000000</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>1438000000</v>
-      </c>
-      <c r="F40" s="3" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Selling And Marketing Expense</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="n">
-        <v>858000000</v>
-      </c>
-      <c r="C41" s="3" t="n">
-        <v>836000000</v>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>776000000</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>703000000</v>
-      </c>
-      <c r="F41" s="3" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>General And Administrative Expense</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="n">
-        <v>910000000</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>961000000</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>852000000</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>735000000</v>
-      </c>
-      <c r="F42" s="3" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Other Gand A</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="n">
-        <v>910000000</v>
-      </c>
-      <c r="C43" s="3" t="n">
-        <v>961000000</v>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>852000000</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>735000000</v>
-      </c>
-      <c r="F43" s="3" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="n">
-        <v>13808000000</v>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>12897000000</v>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>12384000000</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>11993000000</v>
-      </c>
-      <c r="F44" s="3" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Cost Of Revenue</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="n">
-        <v>14560000000</v>
-      </c>
-      <c r="C45" s="3" t="n">
-        <v>14279000000</v>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>14133000000</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>13792000000</v>
-      </c>
-      <c r="F45" s="3" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="n">
-        <v>28368000000</v>
-      </c>
-      <c r="C46" s="3" t="n">
-        <v>27176000000</v>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>26517000000</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>25785000000</v>
-      </c>
-      <c r="F46" s="3" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Operating Revenue</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="n">
-        <v>28368000000</v>
-      </c>
-      <c r="C47" s="3" t="n">
-        <v>27176000000</v>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>26517000000</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>25785000000</v>
-      </c>
-      <c r="F47" s="3" t="n"/>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1775,27 +1289,27 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2024-10-31</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-04-30</t>
+          <t>2022-10-31</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-01-31</t>
+          <t>2021-10-31</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1320,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>-34377147.766323</v>
+        <v>-44345000</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -1815,11 +1329,9 @@
         <v>0</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>564000</v>
+      </c>
+      <c r="F2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1828,20 +1340,18 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0.129725</v>
+        <v>0.245</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.163211</v>
+        <v>0.12</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0.306</v>
+        <v>0.111</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
+        <v>0.141</v>
+      </c>
+      <c r="F3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1850,20 +1360,18 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2789000000</v>
+        <v>10156000000</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2452000000</v>
+        <v>8791000000</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2742000000</v>
+        <v>8469000000</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>2493000000</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>2288000000</v>
-      </c>
+        <v>8267000000</v>
+      </c>
+      <c r="F4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1872,14 +1380,18 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>-265000000</v>
-      </c>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
+        <v>-181000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1888,14 +1400,18 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>-265000000</v>
-      </c>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n">
+        <v>-181000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1904,20 +1420,18 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1926,20 +1440,18 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>127000000</v>
+        <v>435000000</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>114000000</v>
+        <v>392000000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>113000000</v>
+        <v>515000000</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>103000000</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>105000000</v>
-      </c>
+        <v>444000000</v>
+      </c>
+      <c r="F8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1948,20 +1460,18 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>3577000000</v>
+        <v>14560000000</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>3535000000</v>
+        <v>14279000000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>3740000000</v>
+        <v>14133000000</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>3615000000</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>3670000000</v>
-      </c>
+        <v>13792000000</v>
+      </c>
+      <c r="F9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1970,20 +1480,18 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2524000000</v>
+        <v>9975000000</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2452000000</v>
+        <v>8791000000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>2742000000</v>
+        <v>8469000000</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>2493000000</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>2288000000</v>
-      </c>
+        <v>8271000000</v>
+      </c>
+      <c r="F10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1992,20 +1500,18 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>2397000000</v>
+        <v>9540000000</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>2338000000</v>
+        <v>8399000000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2629000000</v>
+        <v>7954000000</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>2390000000</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>2183000000</v>
-      </c>
+        <v>7827000000</v>
+      </c>
+      <c r="F11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2014,20 +1520,18 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>497000000</v>
+        <v>982000000</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>555000000</v>
+        <v>285000000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>330000000</v>
+        <v>62000000</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>153000000</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>-56000000</v>
-      </c>
+        <v>-189000000</v>
+      </c>
+      <c r="F12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2036,20 +1540,18 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>69000000</v>
+        <v>269000000</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>71000000</v>
+        <v>247000000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>66000000</v>
+        <v>238000000</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>64000000</v>
-      </c>
+        <v>228000000</v>
+      </c>
+      <c r="F13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2058,20 +1560,18 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>566000000</v>
+        <v>1251000000</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>626000000</v>
+        <v>532000000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>396000000</v>
+        <v>300000000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>221000000</v>
-      </c>
-      <c r="F14" s="3" t="n">
-        <v>8000000</v>
-      </c>
+        <v>39000000</v>
+      </c>
+      <c r="F14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2080,20 +1580,18 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
-        <v>2256622852.233677</v>
+        <v>7134655000</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6521564000</v>
+      </c>
+      <c r="F15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2102,20 +1600,18 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F16" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2124,20 +1620,18 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>4916000000</v>
+        <v>19898000000</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>4907000000</v>
+        <v>19309000000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5069000000</v>
+        <v>18863000000</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>4931000000</v>
-      </c>
-      <c r="F17" s="3" t="n">
-        <v>4991000000</v>
-      </c>
+        <v>18001000000</v>
+      </c>
+      <c r="F17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2146,20 +1640,18 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>1831000000</v>
+        <v>8289000000</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1712000000</v>
+        <v>7867000000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>2233000000</v>
+        <v>7654000000</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>2169000000</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>2175000000</v>
-      </c>
+        <v>7788000000</v>
+      </c>
+      <c r="F18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2168,20 +1660,18 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>799000000</v>
+        <v>808000000</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>798000000</v>
+        <v>834000000</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>802000000</v>
+        <v>845000000</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>812000000</v>
-      </c>
-      <c r="F19" s="3" t="n">
-        <v>819000000</v>
-      </c>
+        <v>877000000</v>
+      </c>
+      <c r="F19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2190,20 +1680,18 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>793000000</v>
+        <v>804000000</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>794000000</v>
+        <v>827000000</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>798000000</v>
+        <v>840000000</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>809000000</v>
-      </c>
-      <c r="F20" s="3" t="n">
-        <v>814000000</v>
-      </c>
+        <v>871000000</v>
+      </c>
+      <c r="F20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2212,20 +1700,18 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>2.54</v>
+        <v>8.66</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>2.38</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2.22</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="F21" s="3" t="n">
-        <v>1.45</v>
-      </c>
+        <v>7.44</v>
+      </c>
+      <c r="F21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2234,20 +1720,18 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2.55</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2.39</v>
+        <v>8.68</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.23</v>
+        <v>8.16</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>1.46</v>
-      </c>
+        <v>7.49</v>
+      </c>
+      <c r="F22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2256,20 +1740,18 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F23" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2278,20 +1760,18 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F24" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2300,20 +1780,18 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2322,20 +1800,18 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2344,20 +1820,18 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2026000000</v>
+        <v>6998000000</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1897000000</v>
+        <v>7177000000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1779000000</v>
+        <v>6856000000</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2137000000</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>1185000000</v>
-      </c>
+        <v>6525000000</v>
+      </c>
+      <c r="F27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2366,20 +1840,18 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>302000000</v>
+        <v>2273000000</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>370000000</v>
+        <v>975000000</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>784000000</v>
+        <v>860000000</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>185000000</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>934000000</v>
-      </c>
+        <v>1074000000</v>
+      </c>
+      <c r="F28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2388,20 +1860,18 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2328000000</v>
+        <v>9271000000</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2267000000</v>
+        <v>8152000000</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2563000000</v>
+        <v>7716000000</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2322000000</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>2119000000</v>
-      </c>
+        <v>7599000000</v>
+      </c>
+      <c r="F29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2410,12 +1880,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-265000000</v>
+        <v>-181000000</v>
       </c>
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
-      <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n"/>
+      <c r="E30" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>-311000000</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2424,14 +1898,18 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-265000000</v>
-      </c>
-      <c r="C31" s="3" t="n"/>
-      <c r="D31" s="3" t="n"/>
-      <c r="E31" s="3" t="n"/>
-      <c r="F31" s="3" t="n">
+        <v>-181000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2439,13 +1917,13 @@
           <t>Other Special Charges</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>253000000</v>
-      </c>
+      <c r="B32" s="3" t="n"/>
       <c r="C32" s="3" t="n"/>
       <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n"/>
-      <c r="F32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>154000000</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2454,14 +1932,18 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
-        <v>12000000</v>
-      </c>
-      <c r="C33" s="3" t="n"/>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="n"/>
-      <c r="F33" s="3" t="n">
+        <v>181000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="D33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="F33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2470,20 +1952,18 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>497000000</v>
+        <v>982000000</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>555000000</v>
+        <v>285000000</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>330000000</v>
+        <v>62000000</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>153000000</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>-56000000</v>
-      </c>
+        <v>-189000000</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2492,20 +1972,18 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>69000000</v>
+        <v>269000000</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>71000000</v>
+        <v>247000000</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>66000000</v>
+        <v>238000000</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>68000000</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>64000000</v>
-      </c>
+        <v>228000000</v>
+      </c>
+      <c r="F35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2514,20 +1992,18 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>566000000</v>
+        <v>1251000000</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>626000000</v>
+        <v>532000000</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>396000000</v>
+        <v>300000000</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>221000000</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>8000000</v>
-      </c>
+        <v>39000000</v>
+      </c>
+      <c r="F36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2536,20 +2012,18 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
-        <v>2096000000</v>
+        <v>8470000000</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1893000000</v>
+        <v>7867000000</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>2233000000</v>
+        <v>7654000000</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2169000000</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>2175000000</v>
-      </c>
+        <v>7784000000</v>
+      </c>
+      <c r="F37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2558,20 +2032,18 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>1339000000</v>
+        <v>5338000000</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1372000000</v>
+        <v>5030000000</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1329000000</v>
+        <v>4730000000</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1316000000</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>1321000000</v>
-      </c>
+        <v>4209000000</v>
+      </c>
+      <c r="F38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2580,20 +2052,18 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>928000000</v>
+        <v>3570000000</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>917000000</v>
+        <v>3233000000</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>901000000</v>
+        <v>3102000000</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>893000000</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>859000000</v>
-      </c>
+        <v>2771000000</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2602,20 +2072,18 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>411000000</v>
+        <v>1768000000</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>455000000</v>
+        <v>1797000000</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>428000000</v>
+        <v>1628000000</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>423000000</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>462000000</v>
-      </c>
+        <v>1438000000</v>
+      </c>
+      <c r="F40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2624,20 +2092,18 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>222000000</v>
+        <v>858000000</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>212000000</v>
+        <v>836000000</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>224000000</v>
+        <v>776000000</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>216000000</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>206000000</v>
-      </c>
+        <v>703000000</v>
+      </c>
+      <c r="F41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2646,20 +2112,18 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>189000000</v>
+        <v>910000000</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>243000000</v>
+        <v>961000000</v>
       </c>
       <c r="D42" s="3" t="n">
-        <v>204000000</v>
+        <v>852000000</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>207000000</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>256000000</v>
-      </c>
+        <v>735000000</v>
+      </c>
+      <c r="F42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2668,20 +2132,18 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>189000000</v>
+        <v>910000000</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>243000000</v>
+        <v>961000000</v>
       </c>
       <c r="D43" s="3" t="n">
-        <v>204000000</v>
+        <v>852000000</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>207000000</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>256000000</v>
-      </c>
+        <v>735000000</v>
+      </c>
+      <c r="F43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2690,20 +2152,18 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>3435000000</v>
+        <v>13808000000</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>3265000000</v>
+        <v>12897000000</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>3562000000</v>
+        <v>12384000000</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>3485000000</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>3496000000</v>
-      </c>
+        <v>11993000000</v>
+      </c>
+      <c r="F44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2712,20 +2172,18 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>3577000000</v>
+        <v>14560000000</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>3535000000</v>
+        <v>14279000000</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>3740000000</v>
+        <v>14133000000</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>3615000000</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>3670000000</v>
-      </c>
+        <v>13792000000</v>
+      </c>
+      <c r="F45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2734,20 +2192,18 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>7012000000</v>
+        <v>28368000000</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>6800000000</v>
+        <v>27176000000</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>7302000000</v>
+        <v>26517000000</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>7100000000</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>7166000000</v>
-      </c>
+        <v>25785000000</v>
+      </c>
+      <c r="F46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2756,20 +2212,18 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>7012000000</v>
+        <v>28368000000</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>6800000000</v>
+        <v>27176000000</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>7302000000</v>
+        <v>26517000000</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>7100000000</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>7166000000</v>
-      </c>
+        <v>25785000000</v>
+      </c>
+      <c r="F47" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2777,6 +2231,1100 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Tax Effect Of Unusual Items</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>-34377147.766323</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tax Rate For Calcs</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0.129922</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0.129725</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0.163211</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.07967299999999999</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Normalized EBITDA</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>3429000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2789000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2452000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2742000000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2493000000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Total Unusual Items</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-265000000</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Unusual Items Excluding Goodwill</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-265000000</v>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reconciled Depreciation</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>127000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>114000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Reconciled Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>3963000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3577000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>3535000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>3740000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>3615000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>3429000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2524000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2452000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2742000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>2493000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>3294000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>2397000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2338000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2629000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2390000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>702000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>497000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>555000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>153000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>771000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>566000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>626000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>396000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Normalized Income</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2256622852.233677</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing And Discontinued Operation</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>5387000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4916000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4907000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>5069000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>4931000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Total Operating Income As Reported</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>2523000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1831000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1712000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>2233000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>2169000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Diluted Average Shares</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>799000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>799000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>798000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>802000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>812000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Basic Average Shares</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>794000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>793000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>794000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>798000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>809000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Diluted EPS</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Basic EPS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Diluted NI Availto Com Stockholders</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Net Income Continuous Operations</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>2026000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>1897000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>1779000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>2137000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Tax Provision</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>419000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>302000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>370000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>784000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>185000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Pretax Income</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3225000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>2328000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>2267000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>2563000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>2322000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Other Income Expense</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n"/>
+      <c r="C30" s="3" t="n">
+        <v>-265000000</v>
+      </c>
+      <c r="D30" s="3" t="n"/>
+      <c r="E30" s="3" t="n"/>
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Special Income Charges</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-265000000</v>
+      </c>
+      <c r="D31" s="3" t="n"/>
+      <c r="E31" s="3" t="n"/>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
+        <v>253000000</v>
+      </c>
+      <c r="D32" s="3" t="n"/>
+      <c r="E32" s="3" t="n"/>
+      <c r="F32" s="3" t="n"/>
+      <c r="G32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Restructuring And Mergern Acquisition</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Net Non Operating Interest Income Expense</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>702000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>497000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>555000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>153000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Interest Expense Non Operating</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>71000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>68000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Interest Income Non Operating</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>771000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>566000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>626000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>396000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>2523000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>2096000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>1893000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>2233000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>2169000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1424000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>1339000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>1372000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>1329000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>1316000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Research And Development</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1027000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>928000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>917000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>901000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>893000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Selling General And Administration</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>397000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>411000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>455000000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>428000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>423000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Selling And Marketing Expense</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>233000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>222000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>212000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>224000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>216000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>General And Administrative Expense</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>164000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>204000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>207000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Other Gand A</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>164000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>189000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>204000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>207000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>3947000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>3435000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3265000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3562000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>3485000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>3963000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>3577000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>3535000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>3740000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>3615000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>7910000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>7012000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>6800000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>7302000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>7100000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>7910000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7012000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>6800000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>7302000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>7100000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4546,7 +5094,1997 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H82"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1243000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1242000000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1211000000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>1236000000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>1230000000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>793959430</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>793609867</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>793000000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>796642427</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>802498217</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2036959430</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2035609867</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2004000000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2032642427</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2032498217</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>879000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>92000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>7268000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>7190000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>7050000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>6763000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>6670000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>19755000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>17795000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>16482000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>15518000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>14964000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>30364000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>28270000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>26970000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>25767000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>25222000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>13573000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>13296000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>12882000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>11835000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>11712000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>19755000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>17795000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>16482000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>15518000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>14964000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>813000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>637000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>495000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>409000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>23909000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>21717000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>20415000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>19504000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>18961000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>29165000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>28170000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>26870000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>24967000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>24423000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>23909000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>21717000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>20415000000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>19504000000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>18961000000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>23909000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>21717000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>20415000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>19504000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>18961000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-124000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-110000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-110000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-102000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-144000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-124000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-110000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-110000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-102000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-144000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>45780000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>45380000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>45043000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>44186000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>43149000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>59274000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>56888000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>55227000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>53694000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>52280000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>10531000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>10311000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>10333000000</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>10090000000</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>9966000000</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n"/>
+      <c r="C23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3" t="n"/>
+      <c r="F23" s="3" t="n"/>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>16377000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>15927000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>15884000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>14707000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>14671000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>7379000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>8174000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>7885000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>6824000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>6675000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>572000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>539000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>519000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>467000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>422000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>148000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>139000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>151000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>148000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>139000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>151000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>142000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Tradeand Other Payables Non Current</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>704000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>507000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>356000000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>321000000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>5955000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>6989000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>6859000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>5875000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>5790000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>699000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>536000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>404000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>412000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>328000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>5256000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>6453000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>6455000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>5463000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>5462000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>8998000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>7753000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>7999000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>7883000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>7996000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2570000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2472000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>2566000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>2470000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>2491000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>2570000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>2472000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>2566000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>2470000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>2491000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1313000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>201000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>191000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>888000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>880000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>114000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>101000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>88000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>1199000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>799000000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1199000000</v>
+      </c>
+      <c r="C40" s="3" t="n"/>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n">
+        <v>700000000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>700000000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n">
+        <v>700000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Commercial Paper</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n"/>
+      <c r="C41" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>99000000</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>799000000</v>
+      </c>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>966000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>727000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1221000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1109000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>844000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Provisions</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
+        <v>370000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>4126000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>4314000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>3856000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>3417000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>3411000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1151000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1315000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1133000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>1125000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>930000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>2975000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>2999000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>2723000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2292000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>2481000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Dividends Payable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>421000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>365000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>365000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>366000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>369000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>357000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>710000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>380000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>309000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Income Tax Payable</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>357000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>710000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>380000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>309000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>2197000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1924000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1978000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1769000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1803000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>40286000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>37644000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>36299000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>34211000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>33632000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>17715000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>16595000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>15418000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>14493000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>13924000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>1297000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>929000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>806000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>443000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1047000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1178000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1233000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>1288000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1723000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Assets</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>1047000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>1178000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1233000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>1288000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1723000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>5142000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>4968000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>4327000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>4133000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>3638000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>4154000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3922000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>3933000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>3986000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>3997000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>215000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>226000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>238000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>249000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>3824000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>3707000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>3707000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>3748000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>3748000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>6075000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>5598000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>5119000000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>4643000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>4266000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>-4090000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>-4004000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>-3901000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-3987000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>-3894000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>10165000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>9602000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>9020000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>8630000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>8160000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>1860000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1704000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1460000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>1316000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1116000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>3678000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>3462000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>3217000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>3285000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>3101000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>931000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>885000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>855000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>830000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>802000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Buildings And Improvements</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>3137000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>2993000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>2930000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>2662000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>2628000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Land And Improvements</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>559000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>558000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>558000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>537000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>513000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>22571000000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>21049000000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>20881000000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>19718000000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>19708000000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1176000000</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1016000000</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1060000000</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>1069000000</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1063000000</v>
+      </c>
+      <c r="G70" s="3" t="n"/>
+      <c r="H70" s="3" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v>6343000000</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>5997000000</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>5915000000</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>5807000000</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>5656000000</v>
+      </c>
+      <c r="G71" s="3" t="n"/>
+      <c r="H71" s="3" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1277000000</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1227000000</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1208000000</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>1119000000</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1130000000</v>
+      </c>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Work In Process</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v>1109000000</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>951000000</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>914000000</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>925000000</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>909000000</v>
+      </c>
+      <c r="G73" s="3" t="n"/>
+      <c r="H73" s="3" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>3957000000</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3819000000</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>3793000000</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>3763000000</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>3617000000</v>
+      </c>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v>6811000000</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>5525000000</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>5333000000</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>5828000000</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>6242000000</v>
+      </c>
+      <c r="G75" s="3" t="n"/>
+      <c r="H75" s="3" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Taxes Receivable</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>439000000</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>548000000</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>148000000</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v>6372000000</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>4977000000</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>5185000000</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>5772000000</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>6187000000</v>
+      </c>
+      <c r="G77" s="3" t="n"/>
+      <c r="H77" s="3" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>8241000000</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>8511000000</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>8573000000</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>7014000000</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>6747000000</v>
+      </c>
+      <c r="G78" s="3" t="n"/>
+      <c r="H78" s="3" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v>1940000000</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>1293000000</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1332000000</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>1630000000</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>578000000</v>
+      </c>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>6301000000</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>7218000000</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>7241000000</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>5384000000</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>6169000000</v>
+      </c>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="n">
+        <v>4804000000</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>5677000000</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>5822000000</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>3947000000</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>4729000000</v>
+      </c>
+      <c r="G81" s="3" t="n"/>
+      <c r="H81" s="3" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Cash Financial</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>1497000000</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>1541000000</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1419000000</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1437000000</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>1440000000</v>
+      </c>
+      <c r="G82" s="3" t="n"/>
+      <c r="H82" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5822,13 +8360,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5838,6 +8376,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5848,30 +8387,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5884,21 +8428,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1040000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>2043000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>2050000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>1061000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>544000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5907,21 +8452,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-400000000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-337000000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-851000000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-1056000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-1670000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-1318000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5933,18 +8479,19 @@
         <v>-200000000</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>-802000000</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>-100000000</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>-100000000</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-200000000</v>
+        <v>-100000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5953,21 +8500,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>1094000000</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>100000000</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>100000000</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5976,15 +8524,16 @@
         </is>
       </c>
       <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
         <v>132000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n">
         <v>124000000</v>
       </c>
     </row>
@@ -5995,21 +8544,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-635000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-646000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>-785000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>-584000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-510000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>-381000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -6018,21 +8568,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>65000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>68000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>51000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>68000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>52000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -6041,21 +8592,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>538000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>112000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>235000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>436000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>763000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>70000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -6064,21 +8616,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>6359000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>7287000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>7312000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>5454000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>6244000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>6355000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -6087,21 +8640,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>7287000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>7312000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>5454000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>6244000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>6355000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>8113000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -6110,21 +8664,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-928000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-25000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>1858000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-790000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-111000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-1758000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -6133,21 +8688,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-814000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-931000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-831000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-1457000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-1903000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-1786000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6156,21 +8712,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-814000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-931000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-831000000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-1457000000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-1903000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-1786000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6179,21 +8736,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-80000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-229000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>-39000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>-33000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>-142000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6208,15 +8766,16 @@
         <v>-365000000</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>-365000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>-368000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-325000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-326000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6231,15 +8790,16 @@
         <v>-365000000</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>-365000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>-368000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-325000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-326000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6248,21 +8808,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-269000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-337000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-719000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-1056000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-1541000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-1318000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6271,21 +8832,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-400000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-337000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-851000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-1056000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-1670000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-1318000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6294,15 +8856,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>132000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>124000000</v>
       </c>
     </row>
@@ -6313,13 +8876,13 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-100000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>292000000</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -6328,6 +8891,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6336,13 +8900,13 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-100000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>1000000</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -6351,6 +8915,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6362,18 +8927,19 @@
         <v>-200000000</v>
       </c>
       <c r="C23" s="3" t="n">
+        <v>-200000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
         <v>-102000000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>-100000000</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-100000000</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-200000000</v>
+        <v>-100000000</v>
       </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6382,21 +8948,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>200000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>103000000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>100000000</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>100000000</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>200000000</v>
+        <v>100000000</v>
       </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6405,11 +8972,9 @@
         </is>
       </c>
       <c r="B25" s="3" t="n"/>
-      <c r="C25" s="3" t="n">
+      <c r="C25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
         <v>291000000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
@@ -6418,6 +8983,9 @@
         <v>0</v>
       </c>
       <c r="G25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>-90000000</v>
       </c>
     </row>
@@ -6428,11 +8996,9 @@
         </is>
       </c>
       <c r="B26" s="3" t="n"/>
-      <c r="C26" s="3" t="n">
+      <c r="C26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
         <v>-700000000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>0</v>
@@ -6441,6 +9007,9 @@
         <v>0</v>
       </c>
       <c r="G26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3" t="n">
         <v>-90000000</v>
       </c>
     </row>
@@ -6451,13 +9020,14 @@
         </is>
       </c>
       <c r="B27" s="3" t="n"/>
-      <c r="C27" s="3" t="n">
+      <c r="C27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
         <v>991000000</v>
       </c>
-      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n"/>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n">
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6468,21 +9038,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>-959000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-780000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-139000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>-1967000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>221000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-897000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6491,21 +9062,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-959000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-780000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-139000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-1967000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>221000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-897000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6514,15 +9086,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n"/>
-      <c r="C30" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E30" s="3" t="n"/>
+      <c r="E30" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="F30" s="3" t="n"/>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6531,21 +9104,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-155000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>-134000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>646000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-1383000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>699000000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>-488000000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6554,21 +9128,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>2091000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>1143000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>1591000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>793000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>1921000000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>1223000000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6577,21 +9152,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-2246000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-1277000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-945000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-2176000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-1222000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-1711000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6600,7 +9176,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>-175000000</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0</v>
@@ -6609,12 +9185,13 @@
         <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>-28000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6623,7 +9200,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0</v>
+        <v>-175000000</v>
       </c>
       <c r="C35" s="3" t="n">
         <v>0</v>
@@ -6632,12 +9209,13 @@
         <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-28000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6646,21 +9224,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-635000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-646000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>-785000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-584000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-510000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-381000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6669,21 +9248,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>845000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>1686000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>2828000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>2634000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>1571000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>925000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6692,21 +9272,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>845000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>1686000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>2828000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>2634000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>1571000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>925000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6715,21 +9296,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-1497000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-394000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>1258000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>588000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-723000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-1323000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6738,21 +9320,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>-94000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>96000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>39000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>-397000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6761,21 +9344,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-16000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>47000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>48000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>32000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6784,21 +9368,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-240000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>-154000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-83000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>-145000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>115000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6807,21 +9392,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-279000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>719000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>303000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-236000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-229000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6830,21 +9416,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>383000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-279000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>719000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>303000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-236000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-229000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6853,21 +9440,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>539000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-760000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>172000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>227000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>337000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-429000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6876,21 +9464,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>-156000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>481000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>547000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>76000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>-573000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>200000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6899,21 +9488,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>-156000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>481000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>547000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>76000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>-573000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>200000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6922,21 +9512,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>-319000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>-82000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-108000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>-151000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>-155000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>-80000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6945,21 +9536,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-1396000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>208000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>587000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>415000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>-189000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>-764000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6968,21 +9560,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>-1396000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>208000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>587000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>415000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-189000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>-764000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6991,21 +9584,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>-248000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>264000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>508000000</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>-284000000</v>
-      </c>
       <c r="E51" s="3" t="n">
-        <v>-9000000</v>
+        <v>-260000000</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>-5000000</v>
+        <v>-33000000</v>
       </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7014,21 +9608,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>169000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>156000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>158000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>159000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>195000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7037,15 +9632,20 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>-672000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>-466000000</v>
       </c>
-      <c r="C53" s="3" t="n"/>
       <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n"/>
       <c r="F53" s="3" t="n">
+        <v>-76000000</v>
+      </c>
+      <c r="G53" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7054,21 +9654,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>-78000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>-313000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>668000000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7077,21 +9678,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>-78000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>-313000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>668000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7100,21 +9702,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>127000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>114000000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>113000000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>103000000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>105000000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7123,21 +9726,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>127000000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>114000000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>113000000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>103000000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>105000000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7146,28 +9750,29 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>2806000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>2026000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>1897000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>1779000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>2137000000</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>1185000000</v>
-      </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
